--- a/4.evidence/ELC/ITガバナンス・外部委託先レビュー_FY2025.xlsx
+++ b/4.evidence/ELC/ITガバナンス・外部委託先レビュー_FY2025.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITGovernance" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOC1Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUECMapping" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReportLog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,15 +451,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,6 +494,11 @@
           <t>報告先</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>報告記録ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -523,6 +531,11 @@
           <t>経営会議</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -555,6 +568,11 @@
           <t>取締役会</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -564,27 +582,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>情報セキュリティ</t>
+          <t>SOC1/CUEC・情報セキュリティ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>アクセス管理、ログ監視、特権ID、退職者ID停止</t>
+          <t>SOC1例外、CUEC割当、アクセス管理、ログ監視、特権ID、退職者ID停止</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>退職者停止遅延をフォロー</t>
+          <t>CUEC割当済。退職者停止遅延をフォロー</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ITGC-AC-003及びELC-011で是正管理</t>
+          <t>CUECMapping及びITGC-AC-003/ELC-011で管理</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>CFO/監査等委員会</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03</t>
         </is>
       </c>
     </row>
@@ -601,7 +624,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>年度末決算期間の本番変更凍結、緊急変更時のCFO承認</t>
+          <t>年度末決算期間の本番変更凍結、緊急変更時のCFO承認、CUEC対応状況の期末確認</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -611,12 +634,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>変更管理ログと照合予定</t>
+          <t>変更管理ログ、CUECMapping、ReportLogと照合済</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>財務報告連絡会</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-04</t>
         </is>
       </c>
     </row>
@@ -631,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -639,8 +667,10 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,17 +696,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>SOC1例外</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CUEC対応</t>
+          <t>CUEC総数</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>CUEC割当結果</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>結論</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>報告記録ID</t>
         </is>
       </c>
     </row>
@@ -708,12 +748,625 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ユーザアクセス承認、変更依頼承認、障害連絡先を自社ITGCで対応</t>
+          <t>5件すべて自社側統制へ割当済</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>財務報告への未対応リスクなし</t>
+          <t>CUECMapping参照。1件は退職者停止遅延としてELC-011/ITGC-AC-003で是正管理中</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>未割当CUECなし。財務報告への未対応リスクなし</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CUEC ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SOC1該当箇所</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CUEC要求事項</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>自社側統制ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>自社側統制名</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>統制責任者</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>対応状況</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>確認証跡</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>関連不備/フォロー</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>報告記録ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>User Access - UCC1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>利用者登録・権限変更はユーザ企業が承認し、委託先へ正確に依頼する。</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>SAPユーザ登録・変更承認</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部長</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Workflow_UserRegistration_ApprovalHistory_FY2025.csv; UserRegistration_SampleTransactionList_FY2025.xlsx</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>User Access - UCC2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ユーザ企業は定期的に利用者権限をレビューし、不要権限を削除する。</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-002; ITGC-AC-003</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>四半期ユーザアクセスレビュー / 退職者ID停止</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部長</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>user_roles_matrix.xlsx; 内部統制不備・是正措置管理台帳_FY2025.xlsx</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-003としてELC-011で是正管理</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03; RPT-IT-2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Change Management - UCC1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>本番変更はユーザ企業の変更依頼・UAT承認に基づき実施する。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-CM-001; ITGC-CM-002</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>変更要求承認 / UAT承認</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>アプリケーションチームリーダー</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>change_management_log.xlsx; UAT_Approval_Evidence_FY2025.xlsx</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Operations - UCC1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>障害通知先及びエスカレーション先をユーザ企業が維持する。</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-OM-002</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ジョブ・障害監視とエスカレーション</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>インフラチームリーダー</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Zabbix_IncidentLog_FY2025.csv; 財務報告連絡会_開催実績_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Backup - UCC1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>バックアップ対象、保管期間、リストア確認結果をユーザ企業が確認する。</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-OM-001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>バックアップ監視・リストア確認</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>インフラチームリーダー</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>DB13_BackupJobLog_FY2025.csv; DR_RestoreTest_Result_FY2025.xlsx</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>報告記録ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>報告日</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>会議体/報告先</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>報告者</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>報告内容</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>関連CUEC ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>フォローID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>結論/指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>経営会議</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部長</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 IT計画、ERP保守、セキュリティ施策、年度末変更凍結方針</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>四半期進捗を経営会議へ報告する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>取締役会</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CFO / 情報システム部長</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>財務報告関連IT範囲、ITGC/ITAC評価範囲、外部委託SOC1入手予定</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SAP、WMS、連結決算、開示システムを評価範囲に含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CFO/監査等委員会</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部長</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SOC1レビュー結果、CUEC別自社側統制割当、退職者ID停止遅延</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-01,CUEC-02,CUEC-03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-003</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-02関連の退職者停止遅延をELC-011で是正管理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RPT-IT-2025-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>財務報告連絡会</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部長</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>年度末変更凍結、CUEC対応状況、運用・バックアップ証跡確認</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CUEC-02,CUEC-04,CUEC-05</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-003</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>未割当CUECなし。ITGC-AC-003はQ4不備評価へ反映する</t>
         </is>
       </c>
     </row>
